--- a/Assets/Resources/DataFiles/EnemyData/1. ExcelFile/EnemyData.xlsx
+++ b/Assets/Resources/DataFiles/EnemyData/1. ExcelFile/EnemyData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\m\Desktop\Project2\Assets\Resources\DataFiles\EnemyData\1. ExcelFile\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B22655E-7805-420C-9536-98F9FF497CFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEE7ED08-F4E7-49A1-8CBE-CAA28545F634}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EnemyData" sheetId="1" r:id="rId1"/>

--- a/Assets/Resources/DataFiles/EnemyData/1. ExcelFile/EnemyData.xlsx
+++ b/Assets/Resources/DataFiles/EnemyData/1. ExcelFile/EnemyData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\m\Desktop\Project2\Assets\Resources\DataFiles\EnemyData\1. ExcelFile\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEE7ED08-F4E7-49A1-8CBE-CAA28545F634}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D5757A8-7E44-4199-995D-49F4EFCAD13C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EnemyData" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="49">
   <si>
     <t>string</t>
   </si>
@@ -104,10 +104,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>runtimeId</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>SelfDestruct</t>
   </si>
   <si>
@@ -167,10 +163,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>enemy.normal.melee.patrol_machine</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>enemy.normal.selfdestruct.explosion_drone</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -196,6 +188,10 @@
   </si>
   <si>
     <t>enemy.hidden.hidden.moving_coffer</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>enemy.normal.melee.working_machine</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -591,549 +587,518 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P29"/>
+  <dimension ref="A1:O29"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="41.3984375" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.5" style="1" customWidth="1"/>
-    <col min="3" max="3" width="17.3984375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="13.69921875" style="2" customWidth="1"/>
-    <col min="5" max="5" width="11.8984375" style="1" customWidth="1"/>
-    <col min="6" max="6" width="14.09765625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="17" style="1" customWidth="1"/>
-    <col min="8" max="8" width="15.59765625" style="1" customWidth="1"/>
-    <col min="9" max="9" width="17" style="1" customWidth="1"/>
-    <col min="10" max="10" width="11.59765625" style="1" customWidth="1"/>
-    <col min="11" max="12" width="18" style="1" customWidth="1"/>
-    <col min="13" max="13" width="12.8984375" style="1" customWidth="1"/>
-    <col min="14" max="15" width="8.796875" style="1" customWidth="1"/>
-    <col min="16" max="16384" width="8.796875" style="1"/>
+    <col min="2" max="2" width="17.3984375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="13.69921875" style="2" customWidth="1"/>
+    <col min="4" max="4" width="11.8984375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="14.09765625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="17" style="1" customWidth="1"/>
+    <col min="7" max="7" width="15.59765625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="17" style="1" customWidth="1"/>
+    <col min="9" max="9" width="11.59765625" style="1" customWidth="1"/>
+    <col min="10" max="11" width="18" style="1" customWidth="1"/>
+    <col min="12" max="12" width="12.8984375" style="1" customWidth="1"/>
+    <col min="13" max="14" width="8.796875" style="1" customWidth="1"/>
+    <col min="15" max="16384" width="8.796875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="J1" t="s">
+        <v>1</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="N1" t="s">
+        <v>1</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="J2" t="s">
+        <v>12</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="N2" t="s">
+        <v>14</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A3" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3">
+        <v>200</v>
+      </c>
+      <c r="E3">
+        <v>20</v>
+      </c>
+      <c r="F3" s="1">
+        <v>3</v>
+      </c>
+      <c r="G3" s="1">
+        <v>1</v>
+      </c>
+      <c r="H3" s="1">
+        <v>1.2</v>
+      </c>
+      <c r="I3" s="1">
+        <v>2</v>
+      </c>
+      <c r="J3" s="1">
+        <v>2</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+      <c r="L3" s="1">
         <v>0</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="K1" t="s">
-        <v>1</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="O1" t="s">
-        <v>1</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="A2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="K2" t="s">
-        <v>12</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="O2" t="s">
-        <v>14</v>
-      </c>
-      <c r="P2" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="A3" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B3" s="1">
-        <v>1101</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E3">
-        <v>200</v>
-      </c>
-      <c r="F3">
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3">
+        <v>30</v>
+      </c>
+      <c r="O3">
         <v>20</v>
       </c>
-      <c r="G3" s="1">
-        <v>3</v>
-      </c>
-      <c r="H3" s="1">
-        <v>1</v>
-      </c>
-      <c r="I3" s="1">
-        <v>1.2</v>
-      </c>
-      <c r="J3" s="1">
-        <v>2</v>
-      </c>
-      <c r="K3" s="1">
-        <v>2</v>
-      </c>
-      <c r="L3">
-        <v>1</v>
-      </c>
-      <c r="M3" s="1">
-        <v>0</v>
-      </c>
-      <c r="N3">
-        <v>0</v>
-      </c>
-      <c r="O3">
-        <v>30</v>
-      </c>
-      <c r="P3">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A4" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B4" s="1">
-        <v>1201</v>
+      <c r="B4" s="1" t="s">
+        <v>15</v>
       </c>
       <c r="C4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4">
+        <v>150</v>
+      </c>
+      <c r="E4">
         <v>15</v>
       </c>
-      <c r="D4" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E4">
-        <v>150</v>
-      </c>
-      <c r="F4">
+      <c r="F4" s="1">
+        <v>1</v>
+      </c>
+      <c r="G4" s="1">
+        <v>1</v>
+      </c>
+      <c r="H4" s="1">
+        <v>1</v>
+      </c>
+      <c r="I4" s="1">
+        <v>6</v>
+      </c>
+      <c r="J4" s="1">
+        <v>3</v>
+      </c>
+      <c r="K4">
+        <v>0</v>
+      </c>
+      <c r="L4" s="1">
+        <v>5</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4">
+        <v>25</v>
+      </c>
+      <c r="O4">
         <v>15</v>
       </c>
-      <c r="G4" s="1">
-        <v>1</v>
-      </c>
-      <c r="H4" s="1">
-        <v>1</v>
-      </c>
-      <c r="I4" s="1">
-        <v>1</v>
-      </c>
-      <c r="J4" s="1">
-        <v>6</v>
-      </c>
-      <c r="K4" s="1">
-        <v>3</v>
-      </c>
-      <c r="L4">
-        <v>0</v>
-      </c>
-      <c r="M4" s="1">
-        <v>5</v>
-      </c>
-      <c r="N4">
-        <v>0</v>
-      </c>
-      <c r="O4">
-        <v>25</v>
-      </c>
-      <c r="P4">
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A5" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="A5" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B5" s="1">
-        <v>1301</v>
-      </c>
       <c r="C5" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
+      </c>
+      <c r="D5">
+        <v>100</v>
       </c>
       <c r="E5">
         <v>100</v>
       </c>
-      <c r="F5">
-        <v>100</v>
+      <c r="F5" s="1">
+        <v>0</v>
       </c>
       <c r="G5" s="1">
+        <v>1</v>
+      </c>
+      <c r="H5" s="1">
+        <v>1</v>
+      </c>
+      <c r="I5" s="1">
+        <v>3</v>
+      </c>
+      <c r="J5" s="1">
+        <v>1</v>
+      </c>
+      <c r="K5">
+        <v>5</v>
+      </c>
+      <c r="L5" s="1">
         <v>0</v>
       </c>
-      <c r="H5" s="1">
-        <v>1</v>
-      </c>
-      <c r="I5" s="1">
-        <v>1</v>
-      </c>
-      <c r="J5" s="1">
-        <v>3</v>
-      </c>
-      <c r="K5" s="1">
-        <v>1</v>
-      </c>
-      <c r="L5">
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5">
+        <v>10</v>
+      </c>
+      <c r="O5">
         <v>5</v>
       </c>
-      <c r="M5" s="1">
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A6" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D6">
+        <v>260</v>
+      </c>
+      <c r="E6">
+        <v>26</v>
+      </c>
+      <c r="F6" s="1">
+        <v>4</v>
+      </c>
+      <c r="G6" s="1">
+        <v>1</v>
+      </c>
+      <c r="H6" s="1">
+        <v>1.2</v>
+      </c>
+      <c r="I6" s="1">
+        <v>2</v>
+      </c>
+      <c r="J6" s="1">
+        <v>2</v>
+      </c>
+      <c r="K6">
+        <v>1</v>
+      </c>
+      <c r="L6" s="1">
         <v>0</v>
       </c>
-      <c r="N5">
+      <c r="M6">
         <v>0</v>
       </c>
-      <c r="O5">
-        <v>10</v>
-      </c>
-      <c r="P5">
+      <c r="N6">
+        <v>60</v>
+      </c>
+      <c r="O6">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A7" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D7">
+        <v>190</v>
+      </c>
+      <c r="E7">
+        <v>19</v>
+      </c>
+      <c r="F7" s="1">
+        <v>1</v>
+      </c>
+      <c r="G7" s="1">
+        <v>1</v>
+      </c>
+      <c r="H7" s="1">
+        <v>1</v>
+      </c>
+      <c r="I7" s="1">
+        <v>6</v>
+      </c>
+      <c r="J7" s="1">
+        <v>3</v>
+      </c>
+      <c r="K7">
+        <v>0</v>
+      </c>
+      <c r="L7" s="1">
         <v>5</v>
       </c>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="A6" s="3" t="s">
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7">
+        <v>50</v>
+      </c>
+      <c r="O7">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A8" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B6" s="1">
-        <v>2101</v>
-      </c>
-      <c r="C6" s="1" t="s">
+      <c r="B8" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D6" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E6">
-        <v>260</v>
-      </c>
-      <c r="F6">
+      <c r="C8" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="G6" s="1">
-        <v>4</v>
-      </c>
-      <c r="H6" s="1">
-        <v>1</v>
-      </c>
-      <c r="I6" s="1">
-        <v>1.2</v>
-      </c>
-      <c r="J6" s="1">
-        <v>2</v>
-      </c>
-      <c r="K6" s="1">
-        <v>2</v>
-      </c>
-      <c r="L6">
-        <v>1</v>
-      </c>
-      <c r="M6" s="1">
-        <v>0</v>
-      </c>
-      <c r="N6">
-        <v>0</v>
-      </c>
-      <c r="O6">
-        <v>60</v>
-      </c>
-      <c r="P6">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="A7" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B7" s="1">
-        <v>2201</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E7">
-        <v>190</v>
-      </c>
-      <c r="F7">
-        <v>19</v>
-      </c>
-      <c r="G7" s="1">
-        <v>1</v>
-      </c>
-      <c r="H7" s="1">
-        <v>1</v>
-      </c>
-      <c r="I7" s="1">
-        <v>1</v>
-      </c>
-      <c r="J7" s="1">
-        <v>6</v>
-      </c>
-      <c r="K7" s="1">
-        <v>3</v>
-      </c>
-      <c r="L7">
-        <v>0</v>
-      </c>
-      <c r="M7" s="1">
-        <v>5</v>
-      </c>
-      <c r="N7">
-        <v>0</v>
-      </c>
-      <c r="O7">
-        <v>50</v>
-      </c>
-      <c r="P7">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="A8" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="B8" s="1">
-        <v>2301</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>27</v>
+      <c r="D8">
+        <v>130</v>
       </c>
       <c r="E8">
         <v>130</v>
       </c>
-      <c r="F8">
-        <v>130</v>
+      <c r="F8" s="1">
+        <v>0</v>
       </c>
       <c r="G8" s="1">
+        <v>1</v>
+      </c>
+      <c r="H8" s="1">
+        <v>1</v>
+      </c>
+      <c r="I8" s="1">
+        <v>3</v>
+      </c>
+      <c r="J8" s="1">
+        <v>1</v>
+      </c>
+      <c r="K8">
+        <v>5</v>
+      </c>
+      <c r="L8" s="1">
         <v>0</v>
       </c>
-      <c r="H8" s="1">
-        <v>1</v>
-      </c>
-      <c r="I8" s="1">
-        <v>1</v>
-      </c>
-      <c r="J8" s="1">
-        <v>3</v>
-      </c>
-      <c r="K8" s="1">
-        <v>1</v>
-      </c>
-      <c r="L8">
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8">
+        <v>20</v>
+      </c>
+      <c r="O8">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A9" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D9">
+        <v>400</v>
+      </c>
+      <c r="E9">
+        <v>35</v>
+      </c>
+      <c r="F9" s="1">
+        <v>7</v>
+      </c>
+      <c r="G9" s="1">
+        <v>1</v>
+      </c>
+      <c r="H9" s="1">
+        <v>1.2</v>
+      </c>
+      <c r="I9" s="1">
+        <v>2</v>
+      </c>
+      <c r="J9" s="1">
+        <v>2</v>
+      </c>
+      <c r="K9">
+        <v>4</v>
+      </c>
+      <c r="L9" s="1">
         <v>5</v>
       </c>
-      <c r="M8" s="1">
-        <v>0</v>
-      </c>
-      <c r="N8">
-        <v>0</v>
-      </c>
-      <c r="O8">
+      <c r="M9">
+        <v>11</v>
+      </c>
+      <c r="N9">
+        <v>120</v>
+      </c>
+      <c r="O9">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A10" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>20</v>
-      </c>
-      <c r="P8">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="A9" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="B9" s="1">
-        <v>3101</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E9">
-        <v>400</v>
-      </c>
-      <c r="F9">
-        <v>35</v>
-      </c>
-      <c r="G9" s="1">
-        <v>7</v>
-      </c>
-      <c r="H9" s="1">
-        <v>1</v>
-      </c>
-      <c r="I9" s="1">
-        <v>1.2</v>
-      </c>
-      <c r="J9" s="1">
-        <v>2</v>
-      </c>
-      <c r="K9" s="1">
-        <v>2</v>
-      </c>
-      <c r="L9">
-        <v>4</v>
-      </c>
-      <c r="M9" s="1">
-        <v>5</v>
-      </c>
-      <c r="N9">
-        <v>11</v>
-      </c>
-      <c r="O9">
-        <v>120</v>
-      </c>
-      <c r="P9">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="A10" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="B10" s="1">
-        <v>4401</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D10" s="1" t="s">
-        <v>20</v>
+      <c r="D10">
+        <v>800</v>
       </c>
       <c r="E10">
-        <v>800</v>
-      </c>
-      <c r="F10">
         <v>50</v>
       </c>
+      <c r="F10" s="1">
+        <v>10</v>
+      </c>
       <c r="G10" s="1">
+        <v>1</v>
+      </c>
+      <c r="H10" s="1">
+        <v>1</v>
+      </c>
+      <c r="I10" s="1">
+        <v>2</v>
+      </c>
+      <c r="J10" s="1">
+        <v>2</v>
+      </c>
+      <c r="K10">
         <v>10</v>
       </c>
-      <c r="H10" s="1">
-        <v>1</v>
-      </c>
-      <c r="I10" s="1">
-        <v>1</v>
-      </c>
-      <c r="J10" s="1">
-        <v>2</v>
-      </c>
-      <c r="K10" s="1">
-        <v>2</v>
-      </c>
-      <c r="L10">
-        <v>10</v>
-      </c>
-      <c r="M10" s="1">
+      <c r="L10" s="1">
         <v>5</v>
       </c>
+      <c r="M10">
+        <v>101</v>
+      </c>
       <c r="N10">
-        <v>101</v>
+        <v>500</v>
       </c>
       <c r="O10">
         <v>500</v>
       </c>
-      <c r="P10">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A11" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="B11" s="1">
-        <v>5501</v>
+        <v>47</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D11" s="1" t="s">
-        <v>23</v>
+      <c r="D11">
+        <v>400</v>
       </c>
       <c r="E11">
-        <v>400</v>
-      </c>
-      <c r="F11">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="F11" s="1">
+        <v>10</v>
       </c>
       <c r="G11" s="1">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="H11" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I11" s="1">
         <v>1</v>
@@ -1141,39 +1106,36 @@
       <c r="J11" s="1">
         <v>1</v>
       </c>
-      <c r="K11" s="1">
-        <v>1</v>
-      </c>
-      <c r="L11">
+      <c r="K11">
         <v>0</v>
       </c>
-      <c r="M11" s="1">
+      <c r="L11" s="1">
         <v>0</v>
       </c>
+      <c r="M11">
+        <v>1</v>
+      </c>
       <c r="N11">
-        <v>1</v>
+        <v>250</v>
       </c>
       <c r="O11">
-        <v>250</v>
-      </c>
-      <c r="P11">
         <v>200</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A12" s="4"/>
-      <c r="P12"/>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="O12"/>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A13" s="4"/>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A14" s="4"/>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A15" s="4"/>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A16" s="4"/>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.4">
@@ -1225,13 +1187,13 @@
           <x14:formula1>
             <xm:f>ComboBox!$A$2:$A$6</xm:f>
           </x14:formula1>
-          <xm:sqref>C3:C200 D10:D11</xm:sqref>
+          <xm:sqref>B3:B200 C10:C11</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" errorTitle="잘못된 값" error="목록에 없는 값입니다. 드롭다운에서 선택해주세요." xr:uid="{00000000-0002-0000-0000-000001000000}">
           <x14:formula1>
             <xm:f>ComboBox!$B$2:$B$3</xm:f>
           </x14:formula1>
-          <xm:sqref>D3:D9 D12:D200</xm:sqref>
+          <xm:sqref>C3:C9 C12:C200</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -1253,48 +1215,48 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B1" t="s">
         <v>25</v>
       </c>
       <c r="C1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B2" t="s">
         <v>35</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>36</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>37</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>38</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>39</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>40</v>
-      </c>
-      <c r="G2" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.4">
@@ -2034,7 +1996,7 @@
         <v>19</v>
       </c>
       <c r="B4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.4">
@@ -2042,7 +2004,7 @@
         <v>20</v>
       </c>
       <c r="B5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.4">
@@ -2050,7 +2012,7 @@
         <v>23</v>
       </c>
       <c r="B6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Resources/DataFiles/EnemyData/1. ExcelFile/EnemyData.xlsx
+++ b/Assets/Resources/DataFiles/EnemyData/1. ExcelFile/EnemyData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\m\Desktop\Project2\Assets\Resources\DataFiles\EnemyData\1. ExcelFile\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D5757A8-7E44-4199-995D-49F4EFCAD13C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3CB5CBE-5E75-4304-A408-FEA771BE6E71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4560" yWindow="0" windowWidth="14748" windowHeight="12336" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EnemyData" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="51">
   <si>
     <t>string</t>
   </si>
@@ -192,6 +192,14 @@
   </si>
   <si>
     <t>enemy.normal.melee.working_machine</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>playerCount</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hpMultiplierForPlayerCount</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -238,7 +246,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -251,6 +259,9 @@
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1203,7 +1214,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28816B69-B08A-4CD9-ACAD-357F28696E80}">
-  <dimension ref="A1:G35"/>
+  <dimension ref="A1:I35"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="3" max="3" width="12.19921875" bestFit="1" customWidth="1"/>
@@ -1211,9 +1222,10 @@
     <col min="5" max="5" width="12.69921875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="15" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.19921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>30</v>
       </c>
@@ -1235,8 +1247,14 @@
       <c r="G1" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="H1" t="s">
+        <v>25</v>
+      </c>
+      <c r="I1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>34</v>
       </c>
@@ -1258,8 +1276,14 @@
       <c r="G2" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="H2" t="s">
+        <v>49</v>
+      </c>
+      <c r="I2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A3" s="5">
         <v>1</v>
       </c>
@@ -1281,8 +1305,14 @@
       <c r="G3" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="H3" s="6">
+        <v>1</v>
+      </c>
+      <c r="I3" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A4" s="5">
         <v>1.3</v>
       </c>
@@ -1304,8 +1334,14 @@
       <c r="G4" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="H4" s="6">
+        <v>2</v>
+      </c>
+      <c r="I4" s="5">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A5" s="5"/>
       <c r="B5">
         <v>3</v>
@@ -1325,8 +1361,14 @@
       <c r="G5" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="H5" s="6">
+        <v>3</v>
+      </c>
+      <c r="I5" s="5">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A6" s="5"/>
       <c r="B6">
         <v>4</v>
@@ -1346,8 +1388,14 @@
       <c r="G6" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="H6" s="6">
+        <v>4</v>
+      </c>
+      <c r="I6" s="5">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A7" s="5"/>
       <c r="B7">
         <v>5</v>
@@ -1368,7 +1416,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A8" s="5"/>
       <c r="B8">
         <v>6</v>
@@ -1389,7 +1437,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A9" s="5"/>
       <c r="B9">
         <v>7</v>
@@ -1410,7 +1458,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A10" s="5"/>
       <c r="B10">
         <v>8</v>
@@ -1431,7 +1479,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A11" s="5"/>
       <c r="B11">
         <v>9</v>
@@ -1452,7 +1500,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A12" s="5"/>
       <c r="B12">
         <v>10</v>
@@ -1473,7 +1521,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A13" s="5"/>
       <c r="B13">
         <v>11</v>
@@ -1494,7 +1542,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A14" s="5"/>
       <c r="B14">
         <v>12</v>
@@ -1515,7 +1563,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A15" s="5"/>
       <c r="B15">
         <v>13</v>
@@ -1536,7 +1584,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A16" s="5"/>
       <c r="B16">
         <v>14</v>

--- a/Assets/Resources/DataFiles/EnemyData/1. ExcelFile/EnemyData.xlsx
+++ b/Assets/Resources/DataFiles/EnemyData/1. ExcelFile/EnemyData.xlsx
@@ -8,21 +8,23 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\m\Desktop\Project2\Assets\Resources\DataFiles\EnemyData\1. ExcelFile\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3CB5CBE-5E75-4304-A408-FEA771BE6E71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{142057AB-65CA-4F83-A051-B25942418F7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4560" yWindow="0" windowWidth="14748" windowHeight="12336" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EnemyData" sheetId="1" r:id="rId1"/>
     <sheet name="FloorStatScale" sheetId="3" r:id="rId2"/>
-    <sheet name="ComboBox" sheetId="2" r:id="rId3"/>
+    <sheet name="difficultyStatScale" sheetId="4" r:id="rId3"/>
+    <sheet name="playerCountStatScale" sheetId="5" r:id="rId4"/>
+    <sheet name="ComboBox" sheetId="2" r:id="rId5"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="54">
   <si>
     <t>string</t>
   </si>
@@ -135,10 +137,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>difficulty</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>floor</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -200,6 +198,22 @@
   </si>
   <si>
     <t>hpMultiplierForPlayerCount</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>string</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>normal</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hard</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>difficultyName</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -712,7 +726,7 @@
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A3" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>15</v>
@@ -806,7 +820,7 @@
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A5" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>15</v>
@@ -853,7 +867,7 @@
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A6" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>17</v>
@@ -900,7 +914,7 @@
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A7" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>17</v>
@@ -947,7 +961,7 @@
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A8" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>17</v>
@@ -994,7 +1008,7 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A9" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>19</v>
@@ -1041,7 +1055,7 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A10" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>20</v>
@@ -1088,7 +1102,7 @@
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A11" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>23</v>
@@ -1214,23 +1228,23 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28816B69-B08A-4CD9-ACAD-357F28696E80}">
-  <dimension ref="A1:I35"/>
+  <dimension ref="A1:F35"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="3" max="3" width="12.19921875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.59765625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.69921875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.19921875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.19921875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.59765625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.69921875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.19921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B1" t="s">
         <v>30</v>
-      </c>
-      <c r="B1" t="s">
-        <v>25</v>
       </c>
       <c r="C1" t="s">
         <v>30</v>
@@ -1244,17 +1258,8 @@
       <c r="F1" t="s">
         <v>30</v>
       </c>
-      <c r="G1" t="s">
-        <v>30</v>
-      </c>
-      <c r="H1" t="s">
-        <v>25</v>
-      </c>
-      <c r="I1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.4">
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>34</v>
       </c>
@@ -1273,21 +1278,12 @@
       <c r="F2" t="s">
         <v>39</v>
       </c>
-      <c r="G2" t="s">
-        <v>40</v>
-      </c>
-      <c r="H2" t="s">
-        <v>49</v>
-      </c>
-      <c r="I2" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A3" s="5">
-        <v>1</v>
-      </c>
-      <c r="B3">
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3" s="5">
         <v>1</v>
       </c>
       <c r="C3" s="5">
@@ -1302,461 +1298,414 @@
       <c r="F3" s="5">
         <v>1</v>
       </c>
-      <c r="G3" s="5">
-        <v>1</v>
-      </c>
-      <c r="H3" s="6">
-        <v>1</v>
-      </c>
-      <c r="I3" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A4" s="5">
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4" s="5">
+        <v>1</v>
+      </c>
+      <c r="C4" s="5">
+        <v>1</v>
+      </c>
+      <c r="D4" s="5">
+        <v>1</v>
+      </c>
+      <c r="E4" s="5">
+        <v>1</v>
+      </c>
+      <c r="F4" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5" s="5">
+        <v>1</v>
+      </c>
+      <c r="C5" s="5">
+        <v>1</v>
+      </c>
+      <c r="D5" s="5">
+        <v>1</v>
+      </c>
+      <c r="E5" s="5">
+        <v>1</v>
+      </c>
+      <c r="F5" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A6">
+        <v>4</v>
+      </c>
+      <c r="B6" s="5">
+        <v>1</v>
+      </c>
+      <c r="C6" s="5">
+        <v>1</v>
+      </c>
+      <c r="D6" s="5">
+        <v>1</v>
+      </c>
+      <c r="E6" s="5">
+        <v>1</v>
+      </c>
+      <c r="F6" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A7">
+        <v>5</v>
+      </c>
+      <c r="B7" s="5">
+        <v>1.2</v>
+      </c>
+      <c r="C7" s="5">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="D7" s="5">
+        <v>1</v>
+      </c>
+      <c r="E7" s="5">
+        <v>1</v>
+      </c>
+      <c r="F7" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A8">
+        <v>6</v>
+      </c>
+      <c r="B8" s="5">
+        <v>1.2</v>
+      </c>
+      <c r="C8" s="5">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="D8" s="5">
+        <v>1</v>
+      </c>
+      <c r="E8" s="5">
+        <v>1</v>
+      </c>
+      <c r="F8" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A9">
+        <v>7</v>
+      </c>
+      <c r="B9" s="5">
+        <v>1.2</v>
+      </c>
+      <c r="C9" s="5">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="D9" s="5">
+        <v>1</v>
+      </c>
+      <c r="E9" s="5">
+        <v>1</v>
+      </c>
+      <c r="F9" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A10">
+        <v>8</v>
+      </c>
+      <c r="B10" s="5">
         <v>1.3</v>
       </c>
-      <c r="B4">
-        <v>2</v>
-      </c>
-      <c r="C4" s="5">
-        <v>1</v>
-      </c>
-      <c r="D4" s="5">
-        <v>1</v>
-      </c>
-      <c r="E4" s="5">
-        <v>1</v>
-      </c>
-      <c r="F4" s="5">
-        <v>1</v>
-      </c>
-      <c r="G4" s="5">
-        <v>1</v>
-      </c>
-      <c r="H4" s="6">
-        <v>2</v>
-      </c>
-      <c r="I4" s="5">
+      <c r="C10" s="5">
+        <v>1.2</v>
+      </c>
+      <c r="D10" s="5">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="E10" s="5">
+        <v>1</v>
+      </c>
+      <c r="F10" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A11">
+        <v>9</v>
+      </c>
+      <c r="B11" s="5">
+        <v>1.3</v>
+      </c>
+      <c r="C11" s="5">
+        <v>1.2</v>
+      </c>
+      <c r="D11" s="5">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="E11" s="5">
+        <v>1</v>
+      </c>
+      <c r="F11" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A12">
+        <v>10</v>
+      </c>
+      <c r="B12" s="5">
+        <v>1.3</v>
+      </c>
+      <c r="C12" s="5">
+        <v>1.2</v>
+      </c>
+      <c r="D12" s="5">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="E12" s="5">
+        <v>1</v>
+      </c>
+      <c r="F12" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A13">
+        <v>11</v>
+      </c>
+      <c r="B13" s="5">
+        <v>1</v>
+      </c>
+      <c r="C13" s="5">
+        <v>1</v>
+      </c>
+      <c r="D13" s="5">
+        <v>1</v>
+      </c>
+      <c r="E13" s="5">
+        <v>1</v>
+      </c>
+      <c r="F13" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A14">
+        <v>12</v>
+      </c>
+      <c r="B14" s="5">
         <v>1.5</v>
       </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A5" s="5"/>
-      <c r="B5">
-        <v>3</v>
-      </c>
-      <c r="C5" s="5">
-        <v>1</v>
-      </c>
-      <c r="D5" s="5">
-        <v>1</v>
-      </c>
-      <c r="E5" s="5">
-        <v>1</v>
-      </c>
-      <c r="F5" s="5">
-        <v>1</v>
-      </c>
-      <c r="G5" s="5">
-        <v>1</v>
-      </c>
-      <c r="H5" s="6">
-        <v>3</v>
-      </c>
-      <c r="I5" s="5">
-        <v>2.1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A6" s="5"/>
-      <c r="B6">
-        <v>4</v>
-      </c>
-      <c r="C6" s="5">
-        <v>1</v>
-      </c>
-      <c r="D6" s="5">
-        <v>1</v>
-      </c>
-      <c r="E6" s="5">
-        <v>1</v>
-      </c>
-      <c r="F6" s="5">
-        <v>1</v>
-      </c>
-      <c r="G6" s="5">
-        <v>1</v>
-      </c>
-      <c r="H6" s="6">
-        <v>4</v>
-      </c>
-      <c r="I6" s="5">
-        <v>2.8</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A7" s="5"/>
-      <c r="B7">
-        <v>5</v>
-      </c>
-      <c r="C7" s="5">
-        <v>1.2</v>
-      </c>
-      <c r="D7" s="5">
+      <c r="C14" s="5">
+        <v>1.3</v>
+      </c>
+      <c r="D14" s="5">
         <v>1.1000000000000001</v>
       </c>
-      <c r="E7" s="5">
-        <v>1</v>
-      </c>
-      <c r="F7" s="5">
-        <v>1</v>
-      </c>
-      <c r="G7" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A8" s="5"/>
-      <c r="B8">
-        <v>6</v>
-      </c>
-      <c r="C8" s="5">
-        <v>1.2</v>
-      </c>
-      <c r="D8" s="5">
+      <c r="E14" s="5">
+        <v>2</v>
+      </c>
+      <c r="F14" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A15">
+        <v>13</v>
+      </c>
+      <c r="B15" s="5">
+        <v>1.5</v>
+      </c>
+      <c r="C15" s="5">
+        <v>1.3</v>
+      </c>
+      <c r="D15" s="5">
         <v>1.1000000000000001</v>
       </c>
-      <c r="E8" s="5">
-        <v>1</v>
-      </c>
-      <c r="F8" s="5">
-        <v>1</v>
-      </c>
-      <c r="G8" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A9" s="5"/>
-      <c r="B9">
-        <v>7</v>
-      </c>
-      <c r="C9" s="5">
-        <v>1.2</v>
-      </c>
-      <c r="D9" s="5">
+      <c r="E15" s="5">
+        <v>2</v>
+      </c>
+      <c r="F15" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A16">
+        <v>14</v>
+      </c>
+      <c r="B16" s="5">
+        <v>1.5</v>
+      </c>
+      <c r="C16" s="5">
+        <v>1.3</v>
+      </c>
+      <c r="D16" s="5">
         <v>1.1000000000000001</v>
       </c>
-      <c r="E9" s="5">
-        <v>1</v>
-      </c>
-      <c r="F9" s="5">
-        <v>1</v>
-      </c>
-      <c r="G9" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A10" s="5"/>
-      <c r="B10">
-        <v>8</v>
-      </c>
-      <c r="C10" s="5">
+      <c r="E16" s="5">
+        <v>2</v>
+      </c>
+      <c r="F16" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A17">
+        <v>15</v>
+      </c>
+      <c r="B17" s="5">
+        <v>1.5</v>
+      </c>
+      <c r="C17" s="5">
         <v>1.3</v>
       </c>
-      <c r="D10" s="5">
-        <v>1.2</v>
-      </c>
-      <c r="E10" s="5">
+      <c r="D17" s="5">
         <v>1.1000000000000001</v>
       </c>
-      <c r="F10" s="5">
-        <v>1</v>
-      </c>
-      <c r="G10" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A11" s="5"/>
-      <c r="B11">
-        <v>9</v>
-      </c>
-      <c r="C11" s="5">
+      <c r="E17" s="5">
+        <v>2</v>
+      </c>
+      <c r="F17" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A18">
+        <v>16</v>
+      </c>
+      <c r="B18" s="5">
+        <v>1.5</v>
+      </c>
+      <c r="C18" s="5">
         <v>1.3</v>
       </c>
-      <c r="D11" s="5">
-        <v>1.2</v>
-      </c>
-      <c r="E11" s="5">
+      <c r="D18" s="5">
         <v>1.1000000000000001</v>
       </c>
-      <c r="F11" s="5">
-        <v>1</v>
-      </c>
-      <c r="G11" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A12" s="5"/>
-      <c r="B12">
-        <v>10</v>
-      </c>
-      <c r="C12" s="5">
+      <c r="E18" s="5">
+        <v>2</v>
+      </c>
+      <c r="F18" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A19">
+        <v>17</v>
+      </c>
+      <c r="B19" s="5">
+        <v>1.5</v>
+      </c>
+      <c r="C19" s="5">
         <v>1.3</v>
       </c>
-      <c r="D12" s="5">
-        <v>1.2</v>
-      </c>
-      <c r="E12" s="5">
+      <c r="D19" s="5">
         <v>1.1000000000000001</v>
       </c>
-      <c r="F12" s="5">
-        <v>1</v>
-      </c>
-      <c r="G12" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A13" s="5"/>
-      <c r="B13">
-        <v>11</v>
-      </c>
-      <c r="C13" s="5">
-        <v>1</v>
-      </c>
-      <c r="D13" s="5">
-        <v>1</v>
-      </c>
-      <c r="E13" s="5">
-        <v>1</v>
-      </c>
-      <c r="F13" s="5">
-        <v>1</v>
-      </c>
-      <c r="G13" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A14" s="5"/>
-      <c r="B14">
-        <v>12</v>
-      </c>
-      <c r="C14" s="5">
+      <c r="E19" s="5">
+        <v>2</v>
+      </c>
+      <c r="F19" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A20">
+        <v>18</v>
+      </c>
+      <c r="B20" s="5">
         <v>1.5</v>
       </c>
-      <c r="D14" s="5">
+      <c r="C20" s="5">
         <v>1.3</v>
       </c>
-      <c r="E14" s="5">
+      <c r="D20" s="5">
         <v>1.1000000000000001</v>
       </c>
-      <c r="F14" s="5">
-        <v>2</v>
-      </c>
-      <c r="G14" s="5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A15" s="5"/>
-      <c r="B15">
-        <v>13</v>
-      </c>
-      <c r="C15" s="5">
+      <c r="E20" s="5">
+        <v>2</v>
+      </c>
+      <c r="F20" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A21">
+        <v>19</v>
+      </c>
+      <c r="B21" s="5">
         <v>1.5</v>
       </c>
-      <c r="D15" s="5">
+      <c r="C21" s="5">
         <v>1.3</v>
       </c>
-      <c r="E15" s="5">
+      <c r="D21" s="5">
         <v>1.1000000000000001</v>
       </c>
-      <c r="F15" s="5">
-        <v>2</v>
-      </c>
-      <c r="G15" s="5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A16" s="5"/>
-      <c r="B16">
-        <v>14</v>
-      </c>
-      <c r="C16" s="5">
+      <c r="E21" s="5">
+        <v>2</v>
+      </c>
+      <c r="F21" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A22">
+        <v>20</v>
+      </c>
+      <c r="B22" s="5">
         <v>1.5</v>
       </c>
-      <c r="D16" s="5">
+      <c r="C22" s="5">
         <v>1.3</v>
       </c>
-      <c r="E16" s="5">
+      <c r="D22" s="5">
         <v>1.1000000000000001</v>
       </c>
-      <c r="F16" s="5">
-        <v>2</v>
-      </c>
-      <c r="G16" s="5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A17" s="5"/>
-      <c r="B17">
-        <v>15</v>
-      </c>
-      <c r="C17" s="5">
+      <c r="E22" s="5">
+        <v>2</v>
+      </c>
+      <c r="F22" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A23">
+        <v>21</v>
+      </c>
+      <c r="B23" s="5">
         <v>1.5</v>
       </c>
-      <c r="D17" s="5">
+      <c r="C23" s="5">
         <v>1.3</v>
       </c>
-      <c r="E17" s="5">
+      <c r="D23" s="5">
         <v>1.1000000000000001</v>
       </c>
-      <c r="F17" s="5">
-        <v>2</v>
-      </c>
-      <c r="G17" s="5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A18" s="5"/>
-      <c r="B18">
-        <v>16</v>
-      </c>
-      <c r="C18" s="5">
-        <v>1.5</v>
-      </c>
-      <c r="D18" s="5">
-        <v>1.3</v>
-      </c>
-      <c r="E18" s="5">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="F18" s="5">
-        <v>2</v>
-      </c>
-      <c r="G18" s="5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A19" s="5"/>
-      <c r="B19">
-        <v>17</v>
-      </c>
-      <c r="C19" s="5">
-        <v>1.5</v>
-      </c>
-      <c r="D19" s="5">
-        <v>1.3</v>
-      </c>
-      <c r="E19" s="5">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="F19" s="5">
-        <v>2</v>
-      </c>
-      <c r="G19" s="5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A20" s="5"/>
-      <c r="B20">
-        <v>18</v>
-      </c>
-      <c r="C20" s="5">
-        <v>1.5</v>
-      </c>
-      <c r="D20" s="5">
-        <v>1.3</v>
-      </c>
-      <c r="E20" s="5">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="F20" s="5">
-        <v>2</v>
-      </c>
-      <c r="G20" s="5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A21" s="5"/>
-      <c r="B21">
-        <v>19</v>
-      </c>
-      <c r="C21" s="5">
-        <v>1.5</v>
-      </c>
-      <c r="D21" s="5">
-        <v>1.3</v>
-      </c>
-      <c r="E21" s="5">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="F21" s="5">
-        <v>2</v>
-      </c>
-      <c r="G21" s="5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A22" s="5"/>
-      <c r="B22">
-        <v>20</v>
-      </c>
-      <c r="C22" s="5">
-        <v>1.5</v>
-      </c>
-      <c r="D22" s="5">
-        <v>1.3</v>
-      </c>
-      <c r="E22" s="5">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="F22" s="5">
-        <v>2</v>
-      </c>
-      <c r="G22" s="5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A23" s="5"/>
-      <c r="B23">
-        <v>21</v>
-      </c>
-      <c r="C23" s="5">
-        <v>1.5</v>
-      </c>
-      <c r="D23" s="5">
-        <v>1.3</v>
-      </c>
       <c r="E23" s="5">
-        <v>1.1000000000000001</v>
+        <v>2</v>
       </c>
       <c r="F23" s="5">
         <v>2</v>
       </c>
-      <c r="G23" s="5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A24" s="5"/>
-      <c r="B24">
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A24">
         <v>22</v>
       </c>
+      <c r="B24" s="5">
+        <v>1</v>
+      </c>
       <c r="C24" s="5">
         <v>1</v>
       </c>
@@ -1769,15 +1718,14 @@
       <c r="F24" s="5">
         <v>1</v>
       </c>
-      <c r="G24" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A25" s="5"/>
-      <c r="B25">
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A25">
         <v>23</v>
       </c>
+      <c r="B25" s="5">
+        <v>2</v>
+      </c>
       <c r="C25" s="5">
         <v>2</v>
       </c>
@@ -1785,20 +1733,19 @@
         <v>2</v>
       </c>
       <c r="E25" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F25" s="5">
         <v>3</v>
       </c>
-      <c r="G25" s="5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A26" s="5"/>
-      <c r="B26">
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A26">
         <v>24</v>
       </c>
+      <c r="B26" s="5">
+        <v>2</v>
+      </c>
       <c r="C26" s="5">
         <v>2</v>
       </c>
@@ -1806,20 +1753,19 @@
         <v>2</v>
       </c>
       <c r="E26" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F26" s="5">
         <v>3</v>
       </c>
-      <c r="G26" s="5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A27" s="5"/>
-      <c r="B27">
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A27">
         <v>25</v>
       </c>
+      <c r="B27" s="5">
+        <v>2</v>
+      </c>
       <c r="C27" s="5">
         <v>2</v>
       </c>
@@ -1827,20 +1773,19 @@
         <v>2</v>
       </c>
       <c r="E27" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F27" s="5">
         <v>3</v>
       </c>
-      <c r="G27" s="5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A28" s="5"/>
-      <c r="B28">
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A28">
         <v>26</v>
       </c>
+      <c r="B28" s="5">
+        <v>2</v>
+      </c>
       <c r="C28" s="5">
         <v>2</v>
       </c>
@@ -1848,20 +1793,19 @@
         <v>2</v>
       </c>
       <c r="E28" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F28" s="5">
         <v>3</v>
       </c>
-      <c r="G28" s="5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A29" s="5"/>
-      <c r="B29">
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A29">
         <v>27</v>
       </c>
+      <c r="B29" s="5">
+        <v>2</v>
+      </c>
       <c r="C29" s="5">
         <v>2</v>
       </c>
@@ -1869,20 +1813,19 @@
         <v>2</v>
       </c>
       <c r="E29" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F29" s="5">
         <v>3</v>
       </c>
-      <c r="G29" s="5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A30" s="5"/>
-      <c r="B30">
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A30">
         <v>28</v>
       </c>
+      <c r="B30" s="5">
+        <v>2</v>
+      </c>
       <c r="C30" s="5">
         <v>2</v>
       </c>
@@ -1890,20 +1833,19 @@
         <v>2</v>
       </c>
       <c r="E30" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F30" s="5">
         <v>3</v>
       </c>
-      <c r="G30" s="5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A31" s="5"/>
-      <c r="B31">
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A31">
         <v>29</v>
       </c>
+      <c r="B31" s="5">
+        <v>2</v>
+      </c>
       <c r="C31" s="5">
         <v>2</v>
       </c>
@@ -1911,20 +1853,19 @@
         <v>2</v>
       </c>
       <c r="E31" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F31" s="5">
         <v>3</v>
       </c>
-      <c r="G31" s="5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A32" s="5"/>
-      <c r="B32">
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A32">
         <v>30</v>
       </c>
+      <c r="B32" s="5">
+        <v>2</v>
+      </c>
       <c r="C32" s="5">
         <v>2</v>
       </c>
@@ -1932,20 +1873,19 @@
         <v>2</v>
       </c>
       <c r="E32" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F32" s="5">
         <v>3</v>
       </c>
-      <c r="G32" s="5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A33" s="5"/>
-      <c r="B33">
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A33">
         <v>31</v>
       </c>
+      <c r="B33" s="5">
+        <v>2</v>
+      </c>
       <c r="C33" s="5">
         <v>2</v>
       </c>
@@ -1953,20 +1893,19 @@
         <v>2</v>
       </c>
       <c r="E33" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F33" s="5">
         <v>3</v>
       </c>
-      <c r="G33" s="5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A34" s="5"/>
-      <c r="B34">
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A34">
         <v>32</v>
       </c>
+      <c r="B34" s="5">
+        <v>2</v>
+      </c>
       <c r="C34" s="5">
         <v>2</v>
       </c>
@@ -1974,20 +1913,19 @@
         <v>2</v>
       </c>
       <c r="E34" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F34" s="5">
         <v>3</v>
       </c>
-      <c r="G34" s="5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A35" s="5"/>
-      <c r="B35">
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A35">
         <v>33</v>
       </c>
+      <c r="B35" s="5">
+        <v>1</v>
+      </c>
       <c r="C35" s="5">
         <v>1</v>
       </c>
@@ -1998,9 +1936,6 @@
         <v>1</v>
       </c>
       <c r="F35" s="5">
-        <v>1</v>
-      </c>
-      <c r="G35" s="5">
         <v>1</v>
       </c>
     </row>
@@ -2011,6 +1946,167 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9DA531F8-2074-4988-ADCB-50E6B6410DC3}">
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="14.19921875" customWidth="1"/>
+    <col min="2" max="2" width="12.19921875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.59765625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.69921875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B3" s="5">
+        <v>1</v>
+      </c>
+      <c r="C3" s="5">
+        <v>1</v>
+      </c>
+      <c r="D3" s="5">
+        <v>1</v>
+      </c>
+      <c r="E3" s="5">
+        <v>1</v>
+      </c>
+      <c r="F3" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A4" t="s">
+        <v>52</v>
+      </c>
+      <c r="B4" s="5">
+        <v>1.3</v>
+      </c>
+      <c r="C4" s="5">
+        <v>1.3</v>
+      </c>
+      <c r="D4" s="5">
+        <v>1.3</v>
+      </c>
+      <c r="E4" s="5">
+        <v>1</v>
+      </c>
+      <c r="F4" s="5">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD8228A8-67AA-46D5-9D4F-0A19E821CDBF}">
+  <dimension ref="A1:B6"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="12.09765625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A3" s="6">
+        <v>1</v>
+      </c>
+      <c r="B3" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A4" s="6">
+        <v>2</v>
+      </c>
+      <c r="B4" s="5">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A5" s="6">
+        <v>3</v>
+      </c>
+      <c r="B5" s="5">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A6" s="6">
+        <v>4</v>
+      </c>
+      <c r="B6" s="5">
+        <v>2.8</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B6"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>

--- a/Assets/Resources/DataFiles/EnemyData/1. ExcelFile/EnemyData.xlsx
+++ b/Assets/Resources/DataFiles/EnemyData/1. ExcelFile/EnemyData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\m\Desktop\Project2\Assets\Resources\DataFiles\EnemyData\1. ExcelFile\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{142057AB-65CA-4F83-A051-B25942418F7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60794F2C-787C-49F3-9335-F5EEE22BB892}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EnemyData" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="56">
   <si>
     <t>string</t>
   </si>
@@ -214,6 +214,14 @@
   </si>
   <si>
     <t>difficultyName</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Boss</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>enemy.boss.boss.GoliathT</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -612,7 +620,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O29"/>
+  <dimension ref="A1:O30"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="41.3984375" style="1" bestFit="1" customWidth="1"/>
@@ -1061,7 +1069,7 @@
         <v>20</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>20</v>
+        <v>54</v>
       </c>
       <c r="D10">
         <v>800</v>
@@ -1102,57 +1110,100 @@
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A11" s="4" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>20</v>
       </c>
       <c r="D11">
-        <v>400</v>
+        <v>1200</v>
       </c>
       <c r="E11">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="F11" s="1">
         <v>10</v>
       </c>
       <c r="G11" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H11" s="1">
         <v>1</v>
       </c>
       <c r="I11" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J11" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K11">
+        <v>12</v>
+      </c>
+      <c r="L11" s="1">
+        <v>5</v>
+      </c>
+      <c r="M11">
+        <v>102</v>
+      </c>
+      <c r="N11">
+        <v>1000</v>
+      </c>
+      <c r="O11">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A12" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D12">
+        <v>400</v>
+      </c>
+      <c r="E12">
+        <v>1</v>
+      </c>
+      <c r="F12" s="1">
+        <v>10</v>
+      </c>
+      <c r="G12" s="1">
+        <v>2</v>
+      </c>
+      <c r="H12" s="1">
+        <v>1</v>
+      </c>
+      <c r="I12" s="1">
+        <v>1</v>
+      </c>
+      <c r="J12" s="1">
+        <v>1</v>
+      </c>
+      <c r="K12">
         <v>0</v>
       </c>
-      <c r="L11" s="1">
+      <c r="L12" s="1">
         <v>0</v>
       </c>
-      <c r="M11">
-        <v>1</v>
-      </c>
-      <c r="N11">
+      <c r="M12">
+        <v>1</v>
+      </c>
+      <c r="N12">
         <v>250</v>
       </c>
-      <c r="O11">
+      <c r="O12">
         <v>200</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="A12" s="4"/>
-      <c r="O12"/>
-    </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="A13" s="4"/>
+      <c r="C13" s="1"/>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A14" s="4"/>
@@ -1164,7 +1215,7 @@
       <c r="A16" s="4"/>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A17" s="3"/>
+      <c r="A17" s="4"/>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A18" s="3"/>
@@ -1173,7 +1224,7 @@
       <c r="A19" s="3"/>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A20" s="4"/>
+      <c r="A20" s="3"/>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A21" s="4"/>
@@ -1201,6 +1252,9 @@
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A29" s="4"/>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A30" s="4"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -1212,13 +1266,13 @@
           <x14:formula1>
             <xm:f>ComboBox!$A$2:$A$6</xm:f>
           </x14:formula1>
-          <xm:sqref>B3:B200 C10:C11</xm:sqref>
+          <xm:sqref>C10:C12 B14:B201 B3:B12</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" errorTitle="잘못된 값" error="목록에 없는 값입니다. 드롭다운에서 선택해주세요." xr:uid="{00000000-0002-0000-0000-000001000000}">
           <x14:formula1>
             <xm:f>ComboBox!$B$2:$B$3</xm:f>
           </x14:formula1>
-          <xm:sqref>C3:C9 C12:C200</xm:sqref>
+          <xm:sqref>C3:C9 C11 C14:C201</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/Assets/Resources/DataFiles/EnemyData/1. ExcelFile/EnemyData.xlsx
+++ b/Assets/Resources/DataFiles/EnemyData/1. ExcelFile/EnemyData.xlsx
@@ -743,13 +743,13 @@
         <v>18</v>
       </c>
       <c r="D3">
-        <v>200</v>
+        <v>260</v>
       </c>
       <c r="E3">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F3" s="1">
-        <v>3</v>
+        <v>39</v>
       </c>
       <c r="G3" s="1">
         <v>1</v>
@@ -790,13 +790,13 @@
         <v>16</v>
       </c>
       <c r="D4">
-        <v>150</v>
+        <v>195</v>
       </c>
       <c r="E4">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F4" s="1">
-        <v>1</v>
+        <v>37</v>
       </c>
       <c r="G4" s="1">
         <v>1</v>
@@ -837,13 +837,13 @@
         <v>26</v>
       </c>
       <c r="D5">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="E5">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="F5" s="1">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="G5" s="1">
         <v>1</v>
@@ -884,13 +884,13 @@
         <v>18</v>
       </c>
       <c r="D6">
-        <v>260</v>
+        <v>338</v>
       </c>
       <c r="E6">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F6" s="1">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="G6" s="1">
         <v>1</v>
@@ -931,13 +931,13 @@
         <v>16</v>
       </c>
       <c r="D7">
-        <v>190</v>
+        <v>247</v>
       </c>
       <c r="E7">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F7" s="1">
-        <v>1</v>
+        <v>37</v>
       </c>
       <c r="G7" s="1">
         <v>1</v>
@@ -978,13 +978,13 @@
         <v>26</v>
       </c>
       <c r="D8">
-        <v>130</v>
+        <v>169</v>
       </c>
       <c r="E8">
-        <v>130</v>
+        <v>143</v>
       </c>
       <c r="F8" s="1">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="G8" s="1">
         <v>1</v>
@@ -1025,13 +1025,13 @@
         <v>18</v>
       </c>
       <c r="D9">
-        <v>400</v>
+        <v>520</v>
       </c>
       <c r="E9">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="F9" s="1">
-        <v>7</v>
+        <v>54</v>
       </c>
       <c r="G9" s="1">
         <v>1</v>
@@ -1072,13 +1072,13 @@
         <v>54</v>
       </c>
       <c r="D10">
-        <v>800</v>
+        <v>1040</v>
       </c>
       <c r="E10">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="F10" s="1">
-        <v>10</v>
+        <v>58</v>
       </c>
       <c r="G10" s="1">
         <v>1</v>
@@ -1119,13 +1119,13 @@
         <v>20</v>
       </c>
       <c r="D11">
-        <v>1200</v>
+        <v>1560</v>
       </c>
       <c r="E11">
-        <v>60</v>
+        <v>81</v>
       </c>
       <c r="F11" s="1">
-        <v>10</v>
+        <v>58</v>
       </c>
       <c r="G11" s="1">
         <v>1</v>
@@ -1166,13 +1166,13 @@
         <v>23</v>
       </c>
       <c r="D12">
-        <v>400</v>
+        <v>520</v>
       </c>
       <c r="E12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F12" s="1">
-        <v>10</v>
+        <v>48</v>
       </c>
       <c r="G12" s="1">
         <v>2</v>

--- a/Assets/Resources/DataFiles/EnemyData/1. ExcelFile/EnemyData.xlsx
+++ b/Assets/Resources/DataFiles/EnemyData/1. ExcelFile/EnemyData.xlsx
@@ -1282,23 +1282,22 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28816B69-B08A-4CD9-ACAD-357F28696E80}">
-  <dimension ref="A1:F35"/>
+  <dimension ref="A1:G38"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="2" max="2" width="12.19921875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.59765625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.69921875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.19921875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.19921875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.59765625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.69921875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>25</v>
       </c>
       <c r="B1" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C1" t="s">
         <v>30</v>
@@ -1312,32 +1311,40 @@
       <c r="F1" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A2" t="s">
+      <c r="G1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>act</t>
+        </is>
+      </c>
+      <c r="B2" t="s">
         <v>34</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>35</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>36</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>37</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>38</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A3">
         <v>1</v>
       </c>
-      <c r="B3" s="5">
+      <c r="B3">
         <v>1</v>
       </c>
       <c r="C3" s="5">
@@ -1352,19 +1359,22 @@
       <c r="F3" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="G3" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A4">
-        <v>2</v>
-      </c>
-      <c r="B4" s="5">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="B4">
+        <v>2</v>
       </c>
       <c r="C4" s="5">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="D4" s="5">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="E4" s="5">
         <v>1</v>
@@ -1372,19 +1382,22 @@
       <c r="F4" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="G4" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A5">
+        <v>1</v>
+      </c>
+      <c r="B5">
         <v>3</v>
       </c>
-      <c r="B5" s="5">
-        <v>1</v>
-      </c>
       <c r="C5" s="5">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="D5" s="5">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="E5" s="5">
         <v>1</v>
@@ -1392,19 +1405,22 @@
       <c r="F5" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="G5" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A6">
+        <v>1</v>
+      </c>
+      <c r="B6">
         <v>4</v>
       </c>
-      <c r="B6" s="5">
-        <v>1</v>
-      </c>
       <c r="C6" s="5">
-        <v>1</v>
+        <v>1.12</v>
       </c>
       <c r="D6" s="5">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="E6" s="5">
         <v>1</v>
@@ -1412,584 +1428,743 @@
       <c r="F6" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="G6" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A7">
+        <v>1</v>
+      </c>
+      <c r="B7">
         <v>5</v>
       </c>
-      <c r="B7" s="5">
+      <c r="C7" s="5">
+        <v>1.16</v>
+      </c>
+      <c r="D7" s="5">
+        <v>1.07</v>
+      </c>
+      <c r="E7" s="5">
+        <v>1</v>
+      </c>
+      <c r="F7" s="5">
+        <v>1</v>
+      </c>
+      <c r="G7" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A8">
+        <v>1</v>
+      </c>
+      <c r="B8">
+        <v>6</v>
+      </c>
+      <c r="C8" s="5">
+        <v>1.19</v>
+      </c>
+      <c r="D8" s="5">
+        <v>1.08</v>
+      </c>
+      <c r="E8" s="5">
+        <v>1</v>
+      </c>
+      <c r="F8" s="5">
+        <v>1</v>
+      </c>
+      <c r="G8" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A9">
+        <v>1</v>
+      </c>
+      <c r="B9">
+        <v>7</v>
+      </c>
+      <c r="C9" s="5">
+        <v>1.23</v>
+      </c>
+      <c r="D9" s="5">
+        <v>1.1</v>
+      </c>
+      <c r="E9" s="5">
+        <v>1</v>
+      </c>
+      <c r="F9" s="5">
+        <v>1</v>
+      </c>
+      <c r="G9" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A10">
+        <v>1</v>
+      </c>
+      <c r="B10">
+        <v>8</v>
+      </c>
+      <c r="C10" s="5">
+        <v>1.27</v>
+      </c>
+      <c r="D10" s="5">
+        <v>1.12</v>
+      </c>
+      <c r="E10" s="5">
+        <v>1</v>
+      </c>
+      <c r="F10" s="5">
+        <v>1</v>
+      </c>
+      <c r="G10" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A11">
+        <v>1</v>
+      </c>
+      <c r="B11">
+        <v>9</v>
+      </c>
+      <c r="C11" s="5">
+        <v>1.31</v>
+      </c>
+      <c r="D11" s="5">
+        <v>1.13</v>
+      </c>
+      <c r="E11" s="5">
+        <v>1</v>
+      </c>
+      <c r="F11" s="5">
+        <v>1</v>
+      </c>
+      <c r="G11" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A12">
+        <v>1</v>
+      </c>
+      <c r="B12">
+        <v>10</v>
+      </c>
+      <c r="C12" s="5">
+        <v>1.35</v>
+      </c>
+      <c r="D12" s="5">
+        <v>1.15</v>
+      </c>
+      <c r="E12" s="5">
+        <v>1</v>
+      </c>
+      <c r="F12" s="5">
+        <v>1</v>
+      </c>
+      <c r="G12" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A13">
+        <v>1</v>
+      </c>
+      <c r="B13">
+        <v>11</v>
+      </c>
+      <c r="C13" s="5">
+        <v>1</v>
+      </c>
+      <c r="D13" s="5">
+        <v>1</v>
+      </c>
+      <c r="E13" s="5">
+        <v>1</v>
+      </c>
+      <c r="F13" s="5">
+        <v>1</v>
+      </c>
+      <c r="G13" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A14">
+        <v>2</v>
+      </c>
+      <c r="B14">
+        <v>1</v>
+      </c>
+      <c r="C14" s="5">
+        <v>1.5</v>
+      </c>
+      <c r="D14" s="5">
         <v>1.2</v>
       </c>
-      <c r="C7" s="5">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="D7" s="5">
-        <v>1</v>
-      </c>
-      <c r="E7" s="5">
-        <v>1</v>
-      </c>
-      <c r="F7" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A8">
+      <c r="E14" s="5">
+        <v>1.05</v>
+      </c>
+      <c r="F14" s="5">
+        <v>1</v>
+      </c>
+      <c r="G14" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A15">
+        <v>2</v>
+      </c>
+      <c r="B15">
+        <v>2</v>
+      </c>
+      <c r="C15" s="5">
+        <v>1.54</v>
+      </c>
+      <c r="D15" s="5">
+        <v>1.21</v>
+      </c>
+      <c r="E15" s="5">
+        <v>1.06</v>
+      </c>
+      <c r="F15" s="5">
+        <v>1</v>
+      </c>
+      <c r="G15" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A16">
+        <v>2</v>
+      </c>
+      <c r="B16">
+        <v>3</v>
+      </c>
+      <c r="C16" s="5">
+        <v>1.58</v>
+      </c>
+      <c r="D16" s="5">
+        <v>1.23</v>
+      </c>
+      <c r="E16" s="5">
+        <v>1.06</v>
+      </c>
+      <c r="F16" s="5">
+        <v>1</v>
+      </c>
+      <c r="G16" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A17">
+        <v>2</v>
+      </c>
+      <c r="B17">
+        <v>4</v>
+      </c>
+      <c r="C17" s="5">
+        <v>1.62</v>
+      </c>
+      <c r="D17" s="5">
+        <v>1.25</v>
+      </c>
+      <c r="E17" s="5">
+        <v>1.06</v>
+      </c>
+      <c r="F17" s="5">
+        <v>1</v>
+      </c>
+      <c r="G17" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A18">
+        <v>2</v>
+      </c>
+      <c r="B18">
+        <v>5</v>
+      </c>
+      <c r="C18" s="5">
+        <v>1.66</v>
+      </c>
+      <c r="D18" s="5">
+        <v>1.26</v>
+      </c>
+      <c r="E18" s="5">
+        <v>1.07</v>
+      </c>
+      <c r="F18" s="5">
+        <v>1</v>
+      </c>
+      <c r="G18" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A19">
+        <v>2</v>
+      </c>
+      <c r="B19">
         <v>6</v>
       </c>
-      <c r="B8" s="5">
-        <v>1.2</v>
-      </c>
-      <c r="C8" s="5">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="D8" s="5">
-        <v>1</v>
-      </c>
-      <c r="E8" s="5">
-        <v>1</v>
-      </c>
-      <c r="F8" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A9">
+      <c r="C19" s="5">
+        <v>1.7</v>
+      </c>
+      <c r="D19" s="5">
+        <v>1.27</v>
+      </c>
+      <c r="E19" s="5">
+        <v>1.08</v>
+      </c>
+      <c r="F19" s="5">
+        <v>1</v>
+      </c>
+      <c r="G19" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A20">
+        <v>2</v>
+      </c>
+      <c r="B20">
         <v>7</v>
       </c>
-      <c r="B9" s="5">
-        <v>1.2</v>
-      </c>
-      <c r="C9" s="5">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="D9" s="5">
-        <v>1</v>
-      </c>
-      <c r="E9" s="5">
-        <v>1</v>
-      </c>
-      <c r="F9" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A10">
+      <c r="C20" s="5">
+        <v>1.74</v>
+      </c>
+      <c r="D20" s="5">
+        <v>1.29</v>
+      </c>
+      <c r="E20" s="5">
+        <v>1.08</v>
+      </c>
+      <c r="F20" s="5">
+        <v>1</v>
+      </c>
+      <c r="G20" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A21">
+        <v>2</v>
+      </c>
+      <c r="B21">
         <v>8</v>
       </c>
-      <c r="B10" s="5">
-        <v>1.3</v>
-      </c>
-      <c r="C10" s="5">
-        <v>1.2</v>
-      </c>
-      <c r="D10" s="5">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="E10" s="5">
-        <v>1</v>
-      </c>
-      <c r="F10" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A11">
+      <c r="C21" s="5">
+        <v>1.78</v>
+      </c>
+      <c r="D21" s="5">
+        <v>1.31</v>
+      </c>
+      <c r="E21" s="5">
+        <v>1.08</v>
+      </c>
+      <c r="F21" s="5">
+        <v>1</v>
+      </c>
+      <c r="G21" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A22">
+        <v>2</v>
+      </c>
+      <c r="B22">
         <v>9</v>
       </c>
-      <c r="B11" s="5">
-        <v>1.3</v>
-      </c>
-      <c r="C11" s="5">
-        <v>1.2</v>
-      </c>
-      <c r="D11" s="5">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="E11" s="5">
-        <v>1</v>
-      </c>
-      <c r="F11" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A12">
+      <c r="C22" s="5">
+        <v>1.82</v>
+      </c>
+      <c r="D22" s="5">
+        <v>1.32</v>
+      </c>
+      <c r="E22" s="5">
+        <v>1.09</v>
+      </c>
+      <c r="F22" s="5">
+        <v>1</v>
+      </c>
+      <c r="G22" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A23">
+        <v>2</v>
+      </c>
+      <c r="B23">
         <v>10</v>
       </c>
-      <c r="B12" s="5">
-        <v>1.3</v>
-      </c>
-      <c r="C12" s="5">
-        <v>1.2</v>
-      </c>
-      <c r="D12" s="5">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="E12" s="5">
-        <v>1</v>
-      </c>
-      <c r="F12" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A13">
+      <c r="C23" s="5">
+        <v>1.86</v>
+      </c>
+      <c r="D23" s="5">
+        <v>1.33</v>
+      </c>
+      <c r="E23" s="5">
+        <v>1.1</v>
+      </c>
+      <c r="F23" s="5">
+        <v>1</v>
+      </c>
+      <c r="G23" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A24">
+        <v>2</v>
+      </c>
+      <c r="B24">
         <v>11</v>
       </c>
-      <c r="B13" s="5">
-        <v>1</v>
-      </c>
-      <c r="C13" s="5">
-        <v>1</v>
-      </c>
-      <c r="D13" s="5">
-        <v>1</v>
-      </c>
-      <c r="E13" s="5">
-        <v>1</v>
-      </c>
-      <c r="F13" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A14">
+      <c r="C24" s="5">
+        <v>1.9</v>
+      </c>
+      <c r="D24" s="5">
+        <v>1.35</v>
+      </c>
+      <c r="E24" s="5">
+        <v>1.1</v>
+      </c>
+      <c r="F24" s="5">
+        <v>1</v>
+      </c>
+      <c r="G24" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A25">
+        <v>2</v>
+      </c>
+      <c r="B25">
         <v>12</v>
       </c>
-      <c r="B14" s="5">
+      <c r="C25" s="5">
+        <v>1</v>
+      </c>
+      <c r="D25" s="5">
+        <v>1</v>
+      </c>
+      <c r="E25" s="5">
+        <v>1</v>
+      </c>
+      <c r="F25" s="5">
+        <v>1</v>
+      </c>
+      <c r="G25" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A26">
+        <v>3</v>
+      </c>
+      <c r="B26">
+        <v>1</v>
+      </c>
+      <c r="C26" s="5">
+        <v>2.1</v>
+      </c>
+      <c r="D26" s="5">
+        <v>1.45</v>
+      </c>
+      <c r="E26" s="5">
+        <v>1.1</v>
+      </c>
+      <c r="F26" s="5">
+        <v>1</v>
+      </c>
+      <c r="G26" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A27">
+        <v>3</v>
+      </c>
+      <c r="B27">
+        <v>2</v>
+      </c>
+      <c r="C27" s="5">
+        <v>2.15</v>
+      </c>
+      <c r="D27" s="5">
+        <v>1.47</v>
+      </c>
+      <c r="E27" s="5">
+        <v>1.1</v>
+      </c>
+      <c r="F27" s="5">
+        <v>1</v>
+      </c>
+      <c r="G27" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A28">
+        <v>3</v>
+      </c>
+      <c r="B28">
+        <v>3</v>
+      </c>
+      <c r="C28" s="5">
+        <v>2.19</v>
+      </c>
+      <c r="D28" s="5">
+        <v>1.49</v>
+      </c>
+      <c r="E28" s="5">
+        <v>1.11</v>
+      </c>
+      <c r="F28" s="5">
+        <v>1</v>
+      </c>
+      <c r="G28" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A29">
+        <v>3</v>
+      </c>
+      <c r="B29">
+        <v>4</v>
+      </c>
+      <c r="C29" s="5">
+        <v>2.24</v>
+      </c>
+      <c r="D29" s="5">
         <v>1.5</v>
       </c>
-      <c r="C14" s="5">
-        <v>1.3</v>
-      </c>
-      <c r="D14" s="5">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="E14" s="5">
-        <v>2</v>
-      </c>
-      <c r="F14" s="5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A15">
+      <c r="E29" s="5">
+        <v>1.11</v>
+      </c>
+      <c r="F29" s="5">
+        <v>1</v>
+      </c>
+      <c r="G29" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A30">
+        <v>3</v>
+      </c>
+      <c r="B30">
+        <v>5</v>
+      </c>
+      <c r="C30" s="5">
+        <v>2.28</v>
+      </c>
+      <c r="D30" s="5">
+        <v>1.52</v>
+      </c>
+      <c r="E30" s="5">
+        <v>1.12</v>
+      </c>
+      <c r="F30" s="5">
+        <v>1</v>
+      </c>
+      <c r="G30" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A31">
+        <v>3</v>
+      </c>
+      <c r="B31">
+        <v>6</v>
+      </c>
+      <c r="C31" s="5">
+        <v>2.33</v>
+      </c>
+      <c r="D31" s="5">
+        <v>1.54</v>
+      </c>
+      <c r="E31" s="5">
+        <v>1.12</v>
+      </c>
+      <c r="F31" s="5">
+        <v>1</v>
+      </c>
+      <c r="G31" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A32">
+        <v>3</v>
+      </c>
+      <c r="B32">
+        <v>7</v>
+      </c>
+      <c r="C32" s="5">
+        <v>2.37</v>
+      </c>
+      <c r="D32" s="5">
+        <v>1.56</v>
+      </c>
+      <c r="E32" s="5">
+        <v>1.13</v>
+      </c>
+      <c r="F32" s="5">
+        <v>1</v>
+      </c>
+      <c r="G32" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A33">
+        <v>3</v>
+      </c>
+      <c r="B33">
+        <v>8</v>
+      </c>
+      <c r="C33" s="5">
+        <v>2.42</v>
+      </c>
+      <c r="D33" s="5">
+        <v>1.58</v>
+      </c>
+      <c r="E33" s="5">
+        <v>1.13</v>
+      </c>
+      <c r="F33" s="5">
+        <v>1</v>
+      </c>
+      <c r="G33" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A34">
+        <v>3</v>
+      </c>
+      <c r="B34">
+        <v>9</v>
+      </c>
+      <c r="C34" s="5">
+        <v>2.46</v>
+      </c>
+      <c r="D34" s="5">
+        <v>1.6</v>
+      </c>
+      <c r="E34" s="5">
+        <v>1.14</v>
+      </c>
+      <c r="F34" s="5">
+        <v>1</v>
+      </c>
+      <c r="G34" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A35">
+        <v>3</v>
+      </c>
+      <c r="B35">
+        <v>10</v>
+      </c>
+      <c r="C35" s="5">
+        <v>2.51</v>
+      </c>
+      <c r="D35" s="5">
+        <v>1.61</v>
+      </c>
+      <c r="E35" s="5">
+        <v>1.14</v>
+      </c>
+      <c r="F35" s="5">
+        <v>1</v>
+      </c>
+      <c r="G35" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A36">
+        <v>3</v>
+      </c>
+      <c r="B36">
+        <v>11</v>
+      </c>
+      <c r="C36" s="5">
+        <v>2.55</v>
+      </c>
+      <c r="D36" s="5">
+        <v>1.63</v>
+      </c>
+      <c r="E36" s="5">
+        <v>1.15</v>
+      </c>
+      <c r="F36" s="5">
+        <v>1</v>
+      </c>
+      <c r="G36" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A37">
+        <v>3</v>
+      </c>
+      <c r="B37">
+        <v>12</v>
+      </c>
+      <c r="C37" s="5">
+        <v>2.6</v>
+      </c>
+      <c r="D37" s="5">
+        <v>1.65</v>
+      </c>
+      <c r="E37" s="5">
+        <v>1.15</v>
+      </c>
+      <c r="F37" s="5">
+        <v>1</v>
+      </c>
+      <c r="G37" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A38">
+        <v>3</v>
+      </c>
+      <c r="B38">
         <v>13</v>
       </c>
-      <c r="B15" s="5">
-        <v>1.5</v>
-      </c>
-      <c r="C15" s="5">
-        <v>1.3</v>
-      </c>
-      <c r="D15" s="5">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="E15" s="5">
-        <v>2</v>
-      </c>
-      <c r="F15" s="5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A16">
-        <v>14</v>
-      </c>
-      <c r="B16" s="5">
-        <v>1.5</v>
-      </c>
-      <c r="C16" s="5">
-        <v>1.3</v>
-      </c>
-      <c r="D16" s="5">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="E16" s="5">
-        <v>2</v>
-      </c>
-      <c r="F16" s="5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A17">
-        <v>15</v>
-      </c>
-      <c r="B17" s="5">
-        <v>1.5</v>
-      </c>
-      <c r="C17" s="5">
-        <v>1.3</v>
-      </c>
-      <c r="D17" s="5">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="E17" s="5">
-        <v>2</v>
-      </c>
-      <c r="F17" s="5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A18">
-        <v>16</v>
-      </c>
-      <c r="B18" s="5">
-        <v>1.5</v>
-      </c>
-      <c r="C18" s="5">
-        <v>1.3</v>
-      </c>
-      <c r="D18" s="5">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="E18" s="5">
-        <v>2</v>
-      </c>
-      <c r="F18" s="5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A19">
-        <v>17</v>
-      </c>
-      <c r="B19" s="5">
-        <v>1.5</v>
-      </c>
-      <c r="C19" s="5">
-        <v>1.3</v>
-      </c>
-      <c r="D19" s="5">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="E19" s="5">
-        <v>2</v>
-      </c>
-      <c r="F19" s="5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A20">
-        <v>18</v>
-      </c>
-      <c r="B20" s="5">
-        <v>1.5</v>
-      </c>
-      <c r="C20" s="5">
-        <v>1.3</v>
-      </c>
-      <c r="D20" s="5">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="E20" s="5">
-        <v>2</v>
-      </c>
-      <c r="F20" s="5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A21">
-        <v>19</v>
-      </c>
-      <c r="B21" s="5">
-        <v>1.5</v>
-      </c>
-      <c r="C21" s="5">
-        <v>1.3</v>
-      </c>
-      <c r="D21" s="5">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="E21" s="5">
-        <v>2</v>
-      </c>
-      <c r="F21" s="5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A22">
-        <v>20</v>
-      </c>
-      <c r="B22" s="5">
-        <v>1.5</v>
-      </c>
-      <c r="C22" s="5">
-        <v>1.3</v>
-      </c>
-      <c r="D22" s="5">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="E22" s="5">
-        <v>2</v>
-      </c>
-      <c r="F22" s="5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A23">
-        <v>21</v>
-      </c>
-      <c r="B23" s="5">
-        <v>1.5</v>
-      </c>
-      <c r="C23" s="5">
-        <v>1.3</v>
-      </c>
-      <c r="D23" s="5">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="E23" s="5">
-        <v>2</v>
-      </c>
-      <c r="F23" s="5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A24">
-        <v>22</v>
-      </c>
-      <c r="B24" s="5">
-        <v>1</v>
-      </c>
-      <c r="C24" s="5">
-        <v>1</v>
-      </c>
-      <c r="D24" s="5">
-        <v>1</v>
-      </c>
-      <c r="E24" s="5">
-        <v>1</v>
-      </c>
-      <c r="F24" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A25">
-        <v>23</v>
-      </c>
-      <c r="B25" s="5">
-        <v>2</v>
-      </c>
-      <c r="C25" s="5">
-        <v>2</v>
-      </c>
-      <c r="D25" s="5">
-        <v>2</v>
-      </c>
-      <c r="E25" s="5">
-        <v>3</v>
-      </c>
-      <c r="F25" s="5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A26">
-        <v>24</v>
-      </c>
-      <c r="B26" s="5">
-        <v>2</v>
-      </c>
-      <c r="C26" s="5">
-        <v>2</v>
-      </c>
-      <c r="D26" s="5">
-        <v>2</v>
-      </c>
-      <c r="E26" s="5">
-        <v>3</v>
-      </c>
-      <c r="F26" s="5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A27">
-        <v>25</v>
-      </c>
-      <c r="B27" s="5">
-        <v>2</v>
-      </c>
-      <c r="C27" s="5">
-        <v>2</v>
-      </c>
-      <c r="D27" s="5">
-        <v>2</v>
-      </c>
-      <c r="E27" s="5">
-        <v>3</v>
-      </c>
-      <c r="F27" s="5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A28">
-        <v>26</v>
-      </c>
-      <c r="B28" s="5">
-        <v>2</v>
-      </c>
-      <c r="C28" s="5">
-        <v>2</v>
-      </c>
-      <c r="D28" s="5">
-        <v>2</v>
-      </c>
-      <c r="E28" s="5">
-        <v>3</v>
-      </c>
-      <c r="F28" s="5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A29">
-        <v>27</v>
-      </c>
-      <c r="B29" s="5">
-        <v>2</v>
-      </c>
-      <c r="C29" s="5">
-        <v>2</v>
-      </c>
-      <c r="D29" s="5">
-        <v>2</v>
-      </c>
-      <c r="E29" s="5">
-        <v>3</v>
-      </c>
-      <c r="F29" s="5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A30">
-        <v>28</v>
-      </c>
-      <c r="B30" s="5">
-        <v>2</v>
-      </c>
-      <c r="C30" s="5">
-        <v>2</v>
-      </c>
-      <c r="D30" s="5">
-        <v>2</v>
-      </c>
-      <c r="E30" s="5">
-        <v>3</v>
-      </c>
-      <c r="F30" s="5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A31">
-        <v>29</v>
-      </c>
-      <c r="B31" s="5">
-        <v>2</v>
-      </c>
-      <c r="C31" s="5">
-        <v>2</v>
-      </c>
-      <c r="D31" s="5">
-        <v>2</v>
-      </c>
-      <c r="E31" s="5">
-        <v>3</v>
-      </c>
-      <c r="F31" s="5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A32">
-        <v>30</v>
-      </c>
-      <c r="B32" s="5">
-        <v>2</v>
-      </c>
-      <c r="C32" s="5">
-        <v>2</v>
-      </c>
-      <c r="D32" s="5">
-        <v>2</v>
-      </c>
-      <c r="E32" s="5">
-        <v>3</v>
-      </c>
-      <c r="F32" s="5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A33">
-        <v>31</v>
-      </c>
-      <c r="B33" s="5">
-        <v>2</v>
-      </c>
-      <c r="C33" s="5">
-        <v>2</v>
-      </c>
-      <c r="D33" s="5">
-        <v>2</v>
-      </c>
-      <c r="E33" s="5">
-        <v>3</v>
-      </c>
-      <c r="F33" s="5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A34">
-        <v>32</v>
-      </c>
-      <c r="B34" s="5">
-        <v>2</v>
-      </c>
-      <c r="C34" s="5">
-        <v>2</v>
-      </c>
-      <c r="D34" s="5">
-        <v>2</v>
-      </c>
-      <c r="E34" s="5">
-        <v>3</v>
-      </c>
-      <c r="F34" s="5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A35">
-        <v>33</v>
-      </c>
-      <c r="B35" s="5">
-        <v>1</v>
-      </c>
-      <c r="C35" s="5">
-        <v>1</v>
-      </c>
-      <c r="D35" s="5">
-        <v>1</v>
-      </c>
-      <c r="E35" s="5">
-        <v>1</v>
-      </c>
-      <c r="F35" s="5">
+      <c r="C38" s="5">
+        <v>1</v>
+      </c>
+      <c r="D38" s="5">
+        <v>1</v>
+      </c>
+      <c r="E38" s="5">
+        <v>1</v>
+      </c>
+      <c r="F38" s="5">
+        <v>1</v>
+      </c>
+      <c r="G38" s="5">
         <v>1</v>
       </c>
     </row>

--- a/Assets/Resources/DataFiles/EnemyData/1. ExcelFile/EnemyData.xlsx
+++ b/Assets/Resources/DataFiles/EnemyData/1. ExcelFile/EnemyData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\m\Desktop\Project2\Assets\Resources\DataFiles\EnemyData\1. ExcelFile\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60794F2C-787C-49F3-9335-F5EEE22BB892}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{360A27DB-7FCD-47D8-B4B0-9F2A1C429624}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="58">
   <si>
     <t>string</t>
   </si>
@@ -222,6 +222,13 @@
   </si>
   <si>
     <t>enemy.boss.boss.GoliathT</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>act</t>
+  </si>
+  <si>
+    <t>enemy.boss.boss.MutantZ</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -268,7 +275,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -285,6 +292,9 @@
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1203,7 +1213,51 @@
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="C13" s="1"/>
+      <c r="A13" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D13" s="7">
+        <v>2200</v>
+      </c>
+      <c r="E13" s="7">
+        <v>100</v>
+      </c>
+      <c r="F13" s="1">
+        <v>58</v>
+      </c>
+      <c r="G13" s="1">
+        <v>1</v>
+      </c>
+      <c r="H13" s="1">
+        <v>1</v>
+      </c>
+      <c r="I13" s="1">
+        <v>2</v>
+      </c>
+      <c r="J13" s="1">
+        <v>2</v>
+      </c>
+      <c r="K13">
+        <v>14</v>
+      </c>
+      <c r="L13" s="1">
+        <v>5</v>
+      </c>
+      <c r="M13">
+        <v>103</v>
+      </c>
+      <c r="N13">
+        <v>1500</v>
+      </c>
+      <c r="O13">
+        <v>1500</v>
+      </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A14" s="4"/>
@@ -1266,13 +1320,13 @@
           <x14:formula1>
             <xm:f>ComboBox!$A$2:$A$6</xm:f>
           </x14:formula1>
-          <xm:sqref>C10:C12 B14:B201 B3:B12</xm:sqref>
+          <xm:sqref>C10:C13 B3:B201</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" errorTitle="잘못된 값" error="목록에 없는 값입니다. 드롭다운에서 선택해주세요." xr:uid="{00000000-0002-0000-0000-000001000000}">
           <x14:formula1>
             <xm:f>ComboBox!$B$2:$B$3</xm:f>
           </x14:formula1>
-          <xm:sqref>C3:C9 C11 C14:C201</xm:sqref>
+          <xm:sqref>C3:C9 C11 C13:C201</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -1316,10 +1370,8 @@
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>act</t>
-        </is>
+      <c r="A2" t="s">
+        <v>56</v>
       </c>
       <c r="B2" t="s">
         <v>34</v>
@@ -1417,7 +1469,7 @@
         <v>4</v>
       </c>
       <c r="C6" s="5">
-        <v>1.12</v>
+        <v>1.1200000000000001</v>
       </c>
       <c r="D6" s="5">
         <v>1.05</v>
@@ -1440,7 +1492,7 @@
         <v>5</v>
       </c>
       <c r="C7" s="5">
-        <v>1.16</v>
+        <v>1.1599999999999999</v>
       </c>
       <c r="D7" s="5">
         <v>1.07</v>
@@ -1489,7 +1541,7 @@
         <v>1.23</v>
       </c>
       <c r="D9" s="5">
-        <v>1.1</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="E9" s="5">
         <v>1</v>
@@ -1512,7 +1564,7 @@
         <v>1.27</v>
       </c>
       <c r="D10" s="5">
-        <v>1.12</v>
+        <v>1.1200000000000001</v>
       </c>
       <c r="E10" s="5">
         <v>1</v>
@@ -1535,7 +1587,7 @@
         <v>1.31</v>
       </c>
       <c r="D11" s="5">
-        <v>1.13</v>
+        <v>1.1299999999999999</v>
       </c>
       <c r="E11" s="5">
         <v>1</v>
@@ -1558,7 +1610,7 @@
         <v>1.35</v>
       </c>
       <c r="D12" s="5">
-        <v>1.15</v>
+        <v>1.1499999999999999</v>
       </c>
       <c r="E12" s="5">
         <v>1</v>
@@ -1791,7 +1843,7 @@
         <v>1.32</v>
       </c>
       <c r="E22" s="5">
-        <v>1.09</v>
+        <v>1.0900000000000001</v>
       </c>
       <c r="F22" s="5">
         <v>1</v>
@@ -1814,7 +1866,7 @@
         <v>1.33</v>
       </c>
       <c r="E23" s="5">
-        <v>1.1</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="F23" s="5">
         <v>1</v>
@@ -1837,7 +1889,7 @@
         <v>1.35</v>
       </c>
       <c r="E24" s="5">
-        <v>1.1</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="F24" s="5">
         <v>1</v>
@@ -1883,7 +1935,7 @@
         <v>1.45</v>
       </c>
       <c r="E26" s="5">
-        <v>1.1</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="F26" s="5">
         <v>1</v>
@@ -1906,7 +1958,7 @@
         <v>1.47</v>
       </c>
       <c r="E27" s="5">
-        <v>1.1</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="F27" s="5">
         <v>1</v>
@@ -1929,7 +1981,7 @@
         <v>1.49</v>
       </c>
       <c r="E28" s="5">
-        <v>1.11</v>
+        <v>1.1100000000000001</v>
       </c>
       <c r="F28" s="5">
         <v>1</v>
@@ -1946,13 +1998,13 @@
         <v>4</v>
       </c>
       <c r="C29" s="5">
-        <v>2.24</v>
+        <v>2.2400000000000002</v>
       </c>
       <c r="D29" s="5">
         <v>1.5</v>
       </c>
       <c r="E29" s="5">
-        <v>1.11</v>
+        <v>1.1100000000000001</v>
       </c>
       <c r="F29" s="5">
         <v>1</v>
@@ -1969,13 +2021,13 @@
         <v>5</v>
       </c>
       <c r="C30" s="5">
-        <v>2.28</v>
+        <v>2.2799999999999998</v>
       </c>
       <c r="D30" s="5">
         <v>1.52</v>
       </c>
       <c r="E30" s="5">
-        <v>1.12</v>
+        <v>1.1200000000000001</v>
       </c>
       <c r="F30" s="5">
         <v>1</v>
@@ -1998,7 +2050,7 @@
         <v>1.54</v>
       </c>
       <c r="E31" s="5">
-        <v>1.12</v>
+        <v>1.1200000000000001</v>
       </c>
       <c r="F31" s="5">
         <v>1</v>
@@ -2021,7 +2073,7 @@
         <v>1.56</v>
       </c>
       <c r="E32" s="5">
-        <v>1.13</v>
+        <v>1.1299999999999999</v>
       </c>
       <c r="F32" s="5">
         <v>1</v>
@@ -2044,7 +2096,7 @@
         <v>1.58</v>
       </c>
       <c r="E33" s="5">
-        <v>1.13</v>
+        <v>1.1299999999999999</v>
       </c>
       <c r="F33" s="5">
         <v>1</v>
@@ -2067,7 +2119,7 @@
         <v>1.6</v>
       </c>
       <c r="E34" s="5">
-        <v>1.14</v>
+        <v>1.1399999999999999</v>
       </c>
       <c r="F34" s="5">
         <v>1</v>
@@ -2084,13 +2136,13 @@
         <v>10</v>
       </c>
       <c r="C35" s="5">
-        <v>2.51</v>
+        <v>2.5099999999999998</v>
       </c>
       <c r="D35" s="5">
         <v>1.61</v>
       </c>
       <c r="E35" s="5">
-        <v>1.14</v>
+        <v>1.1399999999999999</v>
       </c>
       <c r="F35" s="5">
         <v>1</v>
@@ -2107,13 +2159,13 @@
         <v>11</v>
       </c>
       <c r="C36" s="5">
-        <v>2.55</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="D36" s="5">
         <v>1.63</v>
       </c>
       <c r="E36" s="5">
-        <v>1.15</v>
+        <v>1.1499999999999999</v>
       </c>
       <c r="F36" s="5">
         <v>1</v>
@@ -2136,7 +2188,7 @@
         <v>1.65</v>
       </c>
       <c r="E37" s="5">
-        <v>1.15</v>
+        <v>1.1499999999999999</v>
       </c>
       <c r="F37" s="5">
         <v>1</v>

--- a/Assets/Resources/DataFiles/EnemyData/1. ExcelFile/EnemyData.xlsx
+++ b/Assets/Resources/DataFiles/EnemyData/1. ExcelFile/EnemyData.xlsx
@@ -1578,10 +1578,10 @@
         <v>11</v>
       </c>
       <c r="C13" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D13" s="5">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="E13" s="5">
         <v>1</v>
@@ -1854,13 +1854,13 @@
         <v>12</v>
       </c>
       <c r="C25" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D25" s="5">
-        <v>1</v>
+        <v>1.35</v>
       </c>
       <c r="E25" s="5">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="F25" s="5">
         <v>1</v>
@@ -2153,13 +2153,13 @@
         <v>13</v>
       </c>
       <c r="C38" s="5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D38" s="5">
-        <v>1</v>
+        <v>1.65</v>
       </c>
       <c r="E38" s="5">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="F38" s="5">
         <v>1</v>
